--- a/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
+++ b/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
@@ -1130,11 +1130,11 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>75–77</t>
+          <t>75–76</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1186,11 +1186,11 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>78–78</t>
+          <t>77–108</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>79–82</t>
+          <t>109–112</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1300,7 +1300,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>83–83</t>
+          <t>113–113</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>84–84</t>
+          <t>114–114</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>85–85</t>
+          <t>115–115</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>86–86</t>
+          <t>116–116</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>87–122</t>
+          <t>117–152</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>123–140</t>
+          <t>153–170</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>141–141</t>
+          <t>171–171</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>142–144</t>
+          <t>172–174</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>145–148</t>
+          <t>175–178</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>149–149</t>
+          <t>179–179</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1876,11 +1876,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>150–154</t>
+          <t>180–181</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>155–156</t>
+          <t>182–183</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1984,11 +1984,11 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>157–157</t>
+          <t>184–185</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>158–160</t>
+          <t>186–188</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>161–161</t>
+          <t>189–189</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>162–170</t>
+          <t>190–198</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>171–176</t>
+          <t>199–204</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>177–225</t>
+          <t>205–253</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>226–228</t>
+          <t>254–256</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>229–232</t>
+          <t>257–260</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>233–234</t>
+          <t>261–262</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>235–235</t>
+          <t>263–263</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>236–238</t>
+          <t>264–266</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>239–239</t>
+          <t>267–267</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>240–240</t>
+          <t>268–268</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>241–257</t>
+          <t>269–285</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>258–260</t>
+          <t>286–288</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>261–263</t>
+          <t>289–291</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>264–265</t>
+          <t>292–293</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>266–266</t>
+          <t>294–294</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3004,7 +3004,7 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>267–267</t>
+          <t>295–295</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>268–268</t>
+          <t>296–296</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3104,7 +3104,7 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>269–269</t>
+          <t>297–297</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>270–279</t>
+          <t>298–307</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>280–280</t>
+          <t>308–308</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>281–283</t>
+          <t>309–311</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>284–288</t>
+          <t>312–316</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>289–289</t>
+          <t>317–317</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>290–290</t>
+          <t>318–318</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>291–326</t>
+          <t>319–354</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>327–328</t>
+          <t>355–356</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>329–338</t>
+          <t>357–366</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>339–343</t>
+          <t>367–371</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>344–348</t>
+          <t>372–376</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>349–353</t>
+          <t>377–381</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>354–360</t>
+          <t>382–388</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>361–361</t>
+          <t>389–389</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>362–367</t>
+          <t>390–395</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>368–368</t>
+          <t>396–396</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>369–369</t>
+          <t>397–397</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>370–370</t>
+          <t>398–398</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>371–371</t>
+          <t>399–399</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>372–375</t>
+          <t>400–403</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>376–376</t>
+          <t>404–404</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>377–378</t>
+          <t>405–406</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>379–379</t>
+          <t>407–407</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>380–384</t>
+          <t>408–418</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>385–385</t>
+          <t>419–419</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>386–389</t>
+          <t>420–423</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>390–391</t>
+          <t>424–425</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>392–397</t>
+          <t>426–431</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>398–403</t>
+          <t>432–437</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>404–406</t>
+          <t>438–440</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>407–408</t>
+          <t>441–442</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>409–410</t>
+          <t>443–444</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>411–414</t>
+          <t>445–448</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>415–421</t>
+          <t>449–455</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>422–425</t>
+          <t>456–459</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>426–427</t>
+          <t>460–461</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>428–429</t>
+          <t>462–463</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>430–431</t>
+          <t>464–465</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>432–468</t>
+          <t>466–502</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>469–473</t>
+          <t>503–507</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5560,11 +5560,11 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>474–474</t>
+          <t>508–518</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>475–478</t>
+          <t>519–522</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>479–486</t>
+          <t>523–530</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>487–492</t>
+          <t>531–536</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>493–498</t>
+          <t>537–542</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>499–500</t>
+          <t>543–544</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>501–502</t>
+          <t>545–546</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>503–507</t>
+          <t>547–551</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>508–509</t>
+          <t>552–553</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>510–511</t>
+          <t>554–555</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>512–514</t>
+          <t>556–558</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>515–517</t>
+          <t>559–561</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>518–520</t>
+          <t>562–564</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>521–523</t>
+          <t>565–567</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>524–526</t>
+          <t>568–570</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>527–529</t>
+          <t>571–573</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>530–532</t>
+          <t>574–576</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>533–535</t>
+          <t>577–579</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>536–538</t>
+          <t>580–582</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>539–541</t>
+          <t>583–585</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>542–545</t>
+          <t>586–589</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>546–549</t>
+          <t>590–593</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>550–554</t>
+          <t>594–598</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>555–559</t>
+          <t>599–603</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>560–561</t>
+          <t>604–605</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>562–572</t>
+          <t>606–616</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>573–586</t>
+          <t>617–630</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>587–592</t>
+          <t>631–636</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>593–595</t>
+          <t>637–639</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>596–601</t>
+          <t>640–645</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>602–602</t>
+          <t>646–646</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>603–605</t>
+          <t>647–649</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>606–606</t>
+          <t>650–650</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>607–608</t>
+          <t>651–652</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>609–614</t>
+          <t>653–658</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7714,7 +7714,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>615–615</t>
+          <t>659–659</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7760,7 +7760,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>616–616</t>
+          <t>660–660</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7806,7 +7806,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>617–617</t>
+          <t>661–661</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7852,7 +7852,7 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>618–618</t>
+          <t>662–662</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>619–669</t>
+          <t>663–713</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>670–703</t>
+          <t>714–747</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>704–743</t>
+          <t>748–787</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>744–767</t>
+          <t>788–811</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>768–872</t>
+          <t>812–916</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8182,7 +8182,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>873–873</t>
+          <t>917–917</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8228,7 +8228,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>874–874</t>
+          <t>918–918</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>875–891</t>
+          <t>919–935</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>892–903</t>
+          <t>936–947</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>904–915</t>
+          <t>948–959</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>916–923</t>
+          <t>960–967</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>924–951</t>
+          <t>968–995</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8558,7 +8558,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>952–952</t>
+          <t>996–996</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8608,7 +8608,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>953–953</t>
+          <t>997–997</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>954–971</t>
+          <t>998–1015</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>972–976</t>
+          <t>1016–1020</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>977–985</t>
+          <t>1021–1029</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>986–987</t>
+          <t>1030–1031</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>988–988</t>
+          <t>1032–1032</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>989–1081</t>
+          <t>1033–1125</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1082–1083</t>
+          <t>1126–1127</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>1084–1092</t>
+          <t>1128–1136</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1093–1127</t>
+          <t>1137–1171</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1128–1163</t>
+          <t>1172–1207</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9260,11 +9260,11 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1164–1166</t>
+          <t>1208–1209</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1167–1169</t>
+          <t>1210–1212</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1170–1171</t>
+          <t>1213–1214</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1172–1264</t>
+          <t>1215–1307</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1265–1357</t>
+          <t>1308–1400</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>1358–1362</t>
+          <t>1401–1405</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1363–1439</t>
+          <t>1406–1482</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1440–1456</t>
+          <t>1483–1499</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1457–1459</t>
+          <t>1500–1502</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>1460–1460</t>
+          <t>1503–1503</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>1461–1462</t>
+          <t>1504–1505</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1463–1467</t>
+          <t>1506–1510</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1468–1470</t>
+          <t>1511–1513</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1471–1547</t>
+          <t>1514–1590</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1548–1548</t>
+          <t>1591–1591</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>1549–1549</t>
+          <t>1592–1592</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1550–1550</t>
+          <t>1593–1593</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>1551–1551</t>
+          <t>1594–1594</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>1552–1627</t>
+          <t>1595–1670</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>1628–1704</t>
+          <t>1671–1747</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>1705–1713</t>
+          <t>1748–1756</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>1714–1715</t>
+          <t>1757–1758</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1716–1716</t>
+          <t>1759–1759</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10672,11 +10672,11 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1717–1718</t>
+          <t>1760–1760</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1719–1794</t>
+          <t>1761–1836</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1795–1800</t>
+          <t>1837–1842</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1801–1801</t>
+          <t>1843–1843</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>1802–1802</t>
+          <t>1844–1844</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>1803–1803</t>
+          <t>1845–1845</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>1804–1804</t>
+          <t>1846–1846</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1805–1805</t>
+          <t>1847–1847</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>1806–1811</t>
+          <t>1848–1853</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1812–1887</t>
+          <t>1854–1929</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1888–1891</t>
+          <t>1930–1933</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1892–1894</t>
+          <t>1934–1936</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1895–1895</t>
+          <t>1937–1937</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1896–1953</t>
+          <t>1938–1995</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>1954–1958</t>
+          <t>1996–2000</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>1959–1959</t>
+          <t>2001–2001</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1960–1962</t>
+          <t>2002–2004</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1963–2051</t>
+          <t>2005–2093</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2052–2053</t>
+          <t>2094–2095</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2054–2054</t>
+          <t>2096–2096</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2055–2093</t>
+          <t>2097–2135</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2094–2103</t>
+          <t>2136–2145</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2104–2108</t>
+          <t>2146–2150</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">

--- a/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
+++ b/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
@@ -1174,10 +1174,14 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1865,11 +1869,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>أسامة زيني</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>قرار تطبيق المادة (46) على السيد/ أسامة الزيني بخصوص طلب الت</t>
@@ -1920,8 +1920,16 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>محضر تفويض المحكمة وكيل السيد/ عدنان تحديث صك أرض الروضة بمو</t>
@@ -1972,7 +1980,11 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
@@ -4352,10 +4364,14 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>أسامة زيني</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4364,11 +4380,11 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>404–404</t>
+          <t>404–440</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4432,7 +4448,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>405–406</t>
+          <t>441–442</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4470,12 +4486,12 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>محكمة الاستئناف</t>
+          <t>المحكمة العليا</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4484,11 +4500,11 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>407–407</t>
+          <t>443–535</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4532,8 +4548,16 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>لائحة المدعي بتفصيل مبلغ الحكم الابتدائي ـ 01-02-1445</t>
@@ -4544,7 +4568,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>408–418</t>
+          <t>536–546</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4600,7 +4624,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>419–419</t>
+          <t>547–547</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4664,7 +4688,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>420–423</t>
+          <t>548–551</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4724,7 +4748,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>424–425</t>
+          <t>552–553</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4784,7 +4808,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>426–431</t>
+          <t>554–559</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4848,7 +4872,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>432–437</t>
+          <t>560–565</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4912,7 +4936,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>438–440</t>
+          <t>566–568</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4972,7 +4996,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>441–442</t>
+          <t>569–570</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5032,7 +5056,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>443–444</t>
+          <t>571–572</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5088,7 +5112,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>445–448</t>
+          <t>573–576</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5152,7 +5176,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>449–455</t>
+          <t>577–583</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5216,7 +5240,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>456–459</t>
+          <t>584–587</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5272,7 +5296,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>460–461</t>
+          <t>588–589</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5336,7 +5360,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>462–463</t>
+          <t>590–591</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5392,7 +5416,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>464–465</t>
+          <t>592–593</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5452,7 +5476,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>466–502</t>
+          <t>594–630</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5508,7 +5532,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>503–507</t>
+          <t>631–635</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5552,8 +5576,16 @@
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>مذكرة من المحامي السديري 20-02-1445 ـ الاعتراض على تقرير ابو</t>
@@ -5564,7 +5596,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>508–518</t>
+          <t>636–646</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5624,7 +5656,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>519–522</t>
+          <t>647–650</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5688,7 +5720,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>523–530</t>
+          <t>651–658</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5752,7 +5784,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>531–536</t>
+          <t>659–664</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5816,7 +5848,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>537–542</t>
+          <t>665–670</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5880,7 +5912,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>543–544</t>
+          <t>671–672</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5944,7 +5976,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>545–546</t>
+          <t>673–674</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6004,7 +6036,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>547–551</t>
+          <t>675–679</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6068,7 +6100,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>552–553</t>
+          <t>680–681</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6132,7 +6164,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>554–555</t>
+          <t>682–683</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6192,7 +6224,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>556–558</t>
+          <t>684–686</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6256,7 +6288,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>559–561</t>
+          <t>687–689</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6316,7 +6348,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>562–564</t>
+          <t>690–692</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6380,7 +6412,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>565–567</t>
+          <t>693–695</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6444,7 +6476,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>568–570</t>
+          <t>696–698</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6508,7 +6540,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>571–573</t>
+          <t>699–701</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6572,7 +6604,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>574–576</t>
+          <t>702–704</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6636,7 +6668,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>577–579</t>
+          <t>705–707</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6700,7 +6732,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>580–582</t>
+          <t>708–710</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6760,7 +6792,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>583–585</t>
+          <t>711–713</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6824,7 +6856,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>586–589</t>
+          <t>714–717</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6884,7 +6916,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>590–593</t>
+          <t>718–721</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6948,7 +6980,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>594–598</t>
+          <t>722–726</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7008,7 +7040,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>599–603</t>
+          <t>727–731</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7072,7 +7104,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>604–605</t>
+          <t>732–733</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7136,7 +7168,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>606–616</t>
+          <t>734–744</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7200,7 +7232,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>617–630</t>
+          <t>745–758</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7264,7 +7296,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>631–636</t>
+          <t>759–764</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7328,7 +7360,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>637–639</t>
+          <t>765–767</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7380,7 +7412,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>640–645</t>
+          <t>768–773</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7436,7 +7468,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>646–646</t>
+          <t>774–774</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7492,7 +7524,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>647–649</t>
+          <t>775–777</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7548,7 +7580,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>650–650</t>
+          <t>778–778</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7608,7 +7640,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>651–652</t>
+          <t>779–780</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7664,7 +7696,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>653–658</t>
+          <t>781–786</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7714,7 +7746,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>659–659</t>
+          <t>787–787</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7760,7 +7792,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>660–660</t>
+          <t>788–788</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7806,7 +7838,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>661–661</t>
+          <t>789–789</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7852,7 +7884,7 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>662–662</t>
+          <t>790–790</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7908,7 +7940,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>663–713</t>
+          <t>791–841</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7964,7 +7996,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>714–747</t>
+          <t>842–875</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8020,7 +8052,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>748–787</t>
+          <t>876–915</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8076,7 +8108,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>788–811</t>
+          <t>916–939</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8132,7 +8164,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>812–916</t>
+          <t>940–1044</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8182,7 +8214,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>917–917</t>
+          <t>1045–1045</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8228,7 +8260,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>918–918</t>
+          <t>1046–1046</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8280,7 +8312,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>919–935</t>
+          <t>1047–1063</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8336,7 +8368,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>936–947</t>
+          <t>1064–1075</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8392,7 +8424,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>948–959</t>
+          <t>1076–1087</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8448,7 +8480,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>960–967</t>
+          <t>1088–1095</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8508,7 +8540,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>968–995</t>
+          <t>1096–1123</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8558,7 +8590,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>996–996</t>
+          <t>1124–1124</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8608,7 +8640,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>997–997</t>
+          <t>1125–1125</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8660,7 +8692,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>998–1015</t>
+          <t>1126–1143</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8716,7 +8748,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1016–1020</t>
+          <t>1144–1148</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8776,7 +8808,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>1021–1029</t>
+          <t>1149–1157</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8836,7 +8868,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>1030–1031</t>
+          <t>1158–1159</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8874,11 +8906,7 @@
           <t>صورة تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>1445/04/30</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
@@ -8896,7 +8924,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>1032–1032</t>
+          <t>1160–1160</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -8960,7 +8988,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>1033–1125</t>
+          <t>1161–1253</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9024,7 +9052,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1126–1127</t>
+          <t>1254–1255</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9084,7 +9112,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>1128–1136</t>
+          <t>1256–1264</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9144,7 +9172,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>1137–1171</t>
+          <t>1265–1299</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9204,7 +9232,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1172–1207</t>
+          <t>1300–1335</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9242,7 +9270,11 @@
           <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>08/04/1445</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
@@ -9264,7 +9296,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1208–1209</t>
+          <t>1336–1337</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9302,7 +9334,11 @@
           <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>16/03/1445</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
@@ -9324,7 +9360,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1210–1212</t>
+          <t>1338–1340</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9384,7 +9420,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1213–1214</t>
+          <t>1341–1342</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9448,7 +9484,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1215–1307</t>
+          <t>1343–1435</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9512,7 +9548,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1308–1400</t>
+          <t>1436–1528</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9576,7 +9612,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>1401–1405</t>
+          <t>1529–1533</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9640,7 +9676,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1406–1482</t>
+          <t>1534–1610</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9704,7 +9740,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1483–1499</t>
+          <t>1611–1627</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9764,7 +9800,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1500–1502</t>
+          <t>1628–1630</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9820,7 +9856,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>1503–1503</t>
+          <t>1631–1631</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9884,7 +9920,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>1504–1505</t>
+          <t>1632–1633</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9948,7 +9984,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>1506–1510</t>
+          <t>1634–1638</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10012,7 +10048,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>1511–1513</t>
+          <t>1639–1641</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10076,7 +10112,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>1514–1590</t>
+          <t>1642–1718</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10136,7 +10172,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1591–1591</t>
+          <t>1719–1719</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10196,7 +10232,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>1592–1592</t>
+          <t>1720–1720</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10241,7 +10277,11 @@
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
           <t>صورة تقديم 21-05-2024 (3)</t>
@@ -10252,7 +10292,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1593–1593</t>
+          <t>1721–1721</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10308,7 +10348,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>1594–1594</t>
+          <t>1722–1722</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10372,7 +10412,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>1595–1670</t>
+          <t>1723–1798</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10432,7 +10472,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>1671–1747</t>
+          <t>1799–1875</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10496,7 +10536,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>1748–1756</t>
+          <t>1876–1884</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10560,7 +10600,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>1757–1758</t>
+          <t>1885–1886</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10616,7 +10656,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>1759–1759</t>
+          <t>1887–1887</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10676,7 +10716,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1760–1760</t>
+          <t>1888–1888</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10740,7 +10780,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1761–1836</t>
+          <t>1889–1964</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10800,7 +10840,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1837–1842</t>
+          <t>1965–1970</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10838,7 +10878,11 @@
           <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>25/12/1442</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
@@ -10852,7 +10896,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>1843–1843</t>
+          <t>1971–1971</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10890,11 +10934,7 @@
           <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1445/01/01</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
@@ -10908,7 +10948,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>1844–1844</t>
+          <t>1972–1972</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10946,18 +10986,10 @@
           <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1445/01/01</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>أسامة زيني</t>
-        </is>
-      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>صفحة 3 من تقديم الشكوى</t>
@@ -10968,7 +11000,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>1845–1845</t>
+          <t>1973–1973</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11009,11 +11041,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>أسامة زيني</t>
-        </is>
-      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>صورة تقديم الشكوى ـ 243138211</t>
@@ -11024,7 +11052,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>1846–1846</t>
+          <t>1974–1974</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11084,7 +11112,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1847–1847</t>
+          <t>1975–1975</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11148,7 +11176,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>1848–1853</t>
+          <t>1976–1981</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11212,7 +11240,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1854–1929</t>
+          <t>1982–2057</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11276,7 +11304,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1930–1933</t>
+          <t>2058–2061</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11336,7 +11364,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1934–1936</t>
+          <t>2062–2064</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11400,7 +11428,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1937–1937</t>
+          <t>2065–2065</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11464,7 +11492,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1938–1995</t>
+          <t>2066–2123</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11528,7 +11556,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>1996–2000</t>
+          <t>2124–2128</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11588,7 +11616,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2001–2001</t>
+          <t>2129–2129</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11648,7 +11676,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2002–2004</t>
+          <t>2130–2132</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11708,7 +11736,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2005–2093</t>
+          <t>2133–2221</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11772,7 +11800,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2094–2095</t>
+          <t>2222–2223</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11836,7 +11864,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2096–2096</t>
+          <t>2224–2224</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11892,7 +11920,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2097–2135</t>
+          <t>2225–2263</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11944,7 +11972,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2136–2145</t>
+          <t>2264–2273</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11996,7 +12024,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2146–2150</t>
+          <t>2274–2278</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">

--- a/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
+++ b/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
@@ -10277,11 +10277,7 @@
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>أسامة زيني</t>
-        </is>
-      </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>صورة تقديم 21-05-2024 (3)</t>

--- a/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
+++ b/zaini_case_audit_output/outputs/package/الفهرس_الموحد.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N196"/>
+  <dimension ref="A1:N226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12035,6 +12035,1806 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>DOC-196</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>حكم ابتدائي ضد الشيخ اسامة زيني - القضية - 42824717 - 01-01-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>01-01-1445</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>حكم ابتدائي ضد الشيخ اسامة زيني - القضية - 42824717 - 01-01-</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>20</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2279–2298</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-196</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jYjqC1mznAUSMVpLmwzmomaDlVSpR467/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>DOC-197</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>صك حكم ابتدائي رفض الالتماس لعدم الاختصاص ـ 42824717 - 01-07-1447 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>01-07-1447</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>صك حكم ابتدائي رفض الالتماس لعدم الاختصاص ـ 42824717 - 01-07</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2299–2300</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-197</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1u8PIQBXWD7vyHWLXcMbzJ3i4n63H1QRF/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>DOC-198</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>13-03-1445</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-144</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>73</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2301–2373</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-198</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ub0rCd1CD38iZBRYw2V5GG4Pg2hiT2c5/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>سليم</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>DOC-199</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ملخص حقوق الملكية.pdf</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>ملخص حقوق الملكية.pdf</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>20</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2374–2393</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-199</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NpF7OxPSOAtOh0rGMo2WylHboEmj5J5N/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>DOC-200</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 10 يوم 07-07-1443 هـ للدعوى رقم 42824717 تمسك المدعي بالغبن و صورية العقد.pdf</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>07-07-1443</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 10 يوم 07-07-1443 هـ للدعوى رقم 42824717 تمسك ا</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>2394–2396</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-200</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MOmCJpbP1JSTPNHDo7wnCpXpJCmuX3Yl/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>DOC-201</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 17 يوم 27-01-1444 هـ للدعوى رقم 42824717 طلب القاضي اصل عقد البيع.pdf</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>27-01-1444</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 17 يوم 27-01-1444 هـ للدعوى رقم 42824717 طلب ال</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2397–2399</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-201</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17gaJ8pLqaw55ceLHlYo4312Kt47vmzaz/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>DOC-202</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 16 يوم 29-12-1443 هـ للدعوى رقم 42824717 الطعن في عقد البيع وطلب اصل العقد.pdf</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>29-12-1443</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ضبط جلسة رقم 16 يوم 29-12-1443 هـ للدعوى رقم 42824717 الطعن </t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>4</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2400–2403</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-202</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1J1tKOvi55-CsxJHUL99CakmRilK10LXL/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>DOC-203</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 16 بتاريخ 09-11-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>09-11-1443</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 16 بتاريخ 09-11-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>6</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2404–2409</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-203</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Ac6bRYCL2dmkfh_v6TwzsVlcGMMOwlvJ/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>DOC-204</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 12 بتاريخ 19-08-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>19-08-1443</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 12 بتاريخ 19-08-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>6</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2410–2415</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-204</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sk4qkXLdx5ATlnEOZYERD0Mjy39JeOwH/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DOC-205</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 19 يوم 22-03-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>22-03-1444</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 19 يوم 22-03-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2416–2418</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-205</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ynqHOzxru-xjSzRNx956ClBhtKWA1xa2/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DOC-206</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 17 يوم 29-12-1443 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>29-12-1443</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 17 يوم 29-12-1443 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>2</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2419–2420</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-206</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UZMGfPH_sD2Fk1GZtDSccB_lBmlwo5ko/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DOC-207</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 1 بتاريخ 03-01-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>03-01-1443</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 1 بتاريخ 03-01-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2421–2423</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-207</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1yquu2X6WHiF95GawtPgtA-RTDIpc8Mcd/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>DOC-208</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 00 يوم 20-02-1445 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>20-02-1445</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 00 يوم 20-02-1445 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>14</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2424–2437</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-208</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1mynWTK4W3_XUslEgUFrpOkq5czgTTYQo/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>DOC-209</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 22 يوم 03-06-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>03-06-1444</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 22 يوم 03-06-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2438–2440</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-209</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Uz_CI6u1W9CLu6Z9YZ_OuvdddvOEXfTO/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>DOC-210</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 10 بتاريخ 07-07-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>07-07-1443</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 10 بتاريخ 07-07-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2441–2443</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-210</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Bu14__JQQSF88My_C3AIpcOkLktFDf0A/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>DOC-211</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 9 بتاريخ 29-06-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>29-06-1443</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 9 بتاريخ 29-06-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>2</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2444–2445</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-211</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1dbdEHHry2SYyZi_v8ChUrsomGSkgKMLK/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>DOC-212</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 11 بتاريخ 28-07-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>28-07-1443</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 11 بتاريخ 28-07-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2446–2448</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-212</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1rxJLq40p-JLw31vU0MDQVzebO-G01oMS/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DOC-213</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 8 بتاريخ 17-05-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>17-05-1443</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 8 بتاريخ 17-05-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2449–2451</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-213</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1IDmNeN429NCQRSIGUAQHKJ-aznGuCGys/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>DOC-214</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 13 بتاريخ 16-10-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>16-10-1443</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 13 بتاريخ 16-10-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2452–2454</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-214</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11FQ1ua0n93eUOIGZ2c8QYmDbqKPfQ_jD/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>DOC-215</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 6 بتاريخ 04-04-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>04-04-1443</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 6 بتاريخ 04-04-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2455–2456</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-215</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16VrbfwMxRHLTE3K2RZk-UFkRCT6zt7dy/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>DOC-216</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 15 بتاريخ 02-11-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>02-11-1443</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 15 بتاريخ 02-11-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2457–2459</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-216</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1hkfSLIlt1CV7iXSojoDV0DWUdUQ3nhJT/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>DOC-217</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 20 يوم 21-04-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>21-04-1444</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 20 يوم 21-04-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>3</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2460–2462</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-217</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1o3gbUf0T-0k2DHnixUjli_gFM_5BHkmF/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>DOC-218</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 4 بتاريخ 28-02-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>28-02-1443</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 4 بتاريخ 28-02-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>3</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2463–2465</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-218</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1kYpVfNZKMHIfJHFa1GvKldMqUh4NGIQF/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>DOC-219</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 2 بتاريخ 23-01-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>23-01-1443</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 2 بتاريخ 23-01-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>2</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>2466–2467</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-219</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12ZykSkxkU8VZrPR9gtE4xMMtEwcOUWA6/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DOC-220</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 5 بتاريخ 20-03-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>20-03-1443</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 5 بتاريخ 20-03-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2468–2470</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-220</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ptMLbcnKqHkbp9bFlL_QuU5BhxDmjPuf/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DOC-221</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 23 يوم 02-07-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>02-07-1444</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 23 يوم 02-07-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>3</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2471–2473</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-221</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1oQqKZgSZmKIfUnGRF0wsCgAmmsrTIUTa/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DOC-222</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 7 بتاريخ 25-04-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>25-04-1443</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 7 بتاريخ 25-04-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>2</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2474–2475</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-222</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UTTWQULs4OBCTZg1QhJl6uak0M6Vl4zT/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>DOC-223</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 3 بتاريخ 14-02-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>14-02-1443</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 3 بتاريخ 14-02-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>3</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2476–2478</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-223</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1n6jZBX4UajjoaQUh0kN6PlwyW2-OTr7Z/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>DOC-224</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 21 يوم 22-05-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>22-05-1444</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 21 يوم 22-05-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>2</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>2479–2480</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-224</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1a67bUpgWMWC15VqA7HwgLZdu0nCdBupB/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>DOC-225</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 14 بتاريخ 25-10-1443هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>25-10-1443</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 14 بتاريخ 25-10-1443هـ للقضية رقم 42824717.pd</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>4</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2481–2484</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>حزمة_الوثائق.html#DOC-225</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1F8edXbcjfBZ928RxuFgI3K-hRcjJnxmC/view?usp=drivesdk</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
